--- a/MATISP_catalogue.xlsx
+++ b/MATISP_catalogue.xlsx
@@ -44746,7 +44746,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>SAC_MED_BLONSTEIN</t>
+          <t>SAC_MED_ALAUX</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
